--- a/data/filtered/china_children.xlsx
+++ b/data/filtered/china_children.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I204"/>
+  <dimension ref="A1:N204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>是否春节档</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>是否国庆档</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>是否五一档</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否暑期档</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>是否普通周末</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>详情链接</t>
         </is>
       </c>
@@ -498,7 +523,22 @@
           <t>1992-02-01</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1418076/</t>
         </is>
@@ -539,7 +579,22 @@
           <t>2013-02-08</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/21359690/</t>
         </is>
@@ -580,7 +635,22 @@
           <t>2018-01-19</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26787574/</t>
         </is>
@@ -621,7 +691,22 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1299103/</t>
         </is>
@@ -662,7 +747,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2132220/</t>
         </is>
@@ -703,7 +803,22 @@
           <t>2012-08-17</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11502154/</t>
         </is>
@@ -744,7 +859,22 @@
           <t>2012-02-02</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10467774/</t>
         </is>
@@ -785,7 +915,22 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1467748/</t>
         </is>
@@ -826,7 +971,22 @@
           <t>2012-06-15</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19976058/</t>
         </is>
@@ -867,7 +1027,22 @@
           <t>2011-07-08</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4812830/</t>
         </is>
@@ -908,7 +1083,22 @@
           <t>2016-10-02</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26887890/</t>
         </is>
@@ -949,7 +1139,22 @@
           <t>2010-01-29</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4082101/</t>
         </is>
@@ -990,7 +1195,22 @@
           <t>1963</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1461964/</t>
         </is>
@@ -1031,7 +1251,22 @@
           <t>2015-10-23</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11537965/</t>
         </is>
@@ -1072,7 +1307,22 @@
           <t>2020-09-06</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30299040/</t>
         </is>
@@ -1113,7 +1363,22 @@
           <t>2019-05-20</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30206431/</t>
         </is>
@@ -1154,7 +1419,22 @@
           <t>1988</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1440283/</t>
         </is>
@@ -1195,7 +1475,22 @@
           <t>2009-10-02</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3724056/</t>
         </is>
@@ -1236,7 +1531,22 @@
           <t>1974-10-01</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1461985/</t>
         </is>
@@ -1277,7 +1587,22 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1528848/</t>
         </is>
@@ -1318,7 +1643,22 @@
           <t>2005-04-07</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1432509/</t>
         </is>
@@ -1359,7 +1699,22 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2361040/</t>
         </is>
@@ -1400,7 +1755,22 @@
           <t>2009-01-16</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3356338/</t>
         </is>
@@ -1441,7 +1811,22 @@
           <t>2017-08-28</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26951953/</t>
         </is>
@@ -1482,7 +1867,22 @@
           <t>2023-07-28</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35869970/</t>
         </is>
@@ -1523,7 +1923,22 @@
           <t>1963</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1482691/</t>
         </is>
@@ -1564,7 +1979,22 @@
           <t>2012-10-21</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11537964/</t>
         </is>
@@ -1605,7 +2035,22 @@
           <t>1954</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1461981/</t>
         </is>
@@ -1646,7 +2091,22 @@
           <t>2023-09-15</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34889288/</t>
         </is>
@@ -1687,7 +2147,22 @@
           <t>2016-06-22</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26827707/</t>
         </is>
@@ -1728,7 +2203,22 @@
           <t>2022-01-15</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35448988/</t>
         </is>
@@ -1769,7 +2259,22 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26635427/</t>
         </is>
@@ -1810,7 +2315,22 @@
           <t>2012-01-12</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/7056398/</t>
         </is>
@@ -1851,7 +2371,22 @@
           <t>2020-07-20</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30337172/</t>
         </is>
@@ -1892,7 +2427,22 @@
           <t>1996-03-14</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1419904/</t>
         </is>
@@ -1933,7 +2483,22 @@
           <t>2014-09-10</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25882279/</t>
         </is>
@@ -1974,7 +2539,22 @@
           <t>2017-11-13</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26841305/</t>
         </is>
@@ -2015,7 +2595,22 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1482688/</t>
         </is>
@@ -2056,7 +2651,22 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2135039/</t>
         </is>
@@ -2097,7 +2707,22 @@
           <t>2018-01-16</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11615929/</t>
         </is>
@@ -2138,7 +2763,22 @@
           <t>2020-11-20</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33427574/</t>
         </is>
@@ -2179,7 +2819,22 @@
           <t>2020-08-07</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/28510273/</t>
         </is>
@@ -2216,7 +2871,22 @@
           <t>2017-11-21</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27205168/</t>
         </is>
@@ -2257,7 +2927,22 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1938923/</t>
         </is>
@@ -2298,7 +2983,22 @@
           <t>2008-09-24</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3193264/</t>
         </is>
@@ -2335,7 +3035,22 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30142123/</t>
         </is>
@@ -2376,7 +3091,22 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35377026/</t>
         </is>
@@ -2417,7 +3147,22 @@
           <t>2025-01-14</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36404113/</t>
         </is>
@@ -2458,7 +3203,22 @@
           <t>2004-09-19</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1309002/</t>
         </is>
@@ -2499,7 +3259,22 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1461396/</t>
         </is>
@@ -2540,7 +3315,22 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3041483/</t>
         </is>
@@ -2581,7 +3371,22 @@
           <t>1963</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1482869/</t>
         </is>
@@ -2622,7 +3427,22 @@
           <t>2013-10-10</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25725249/</t>
         </is>
@@ -2663,7 +3483,22 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2305321/</t>
         </is>
@@ -2704,7 +3539,22 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1484675/</t>
         </is>
@@ -2745,7 +3595,22 @@
           <t>2012-06-28</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10599639/</t>
         </is>
@@ -2786,7 +3651,22 @@
           <t>1958-12-17</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2212633/</t>
         </is>
@@ -2827,7 +3707,22 @@
           <t>2017-01-28</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26831711/</t>
         </is>
@@ -2868,7 +3763,22 @@
           <t>2018-05-07</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26933248/</t>
         </is>
@@ -2909,7 +3819,22 @@
           <t>2013-01-29</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10569022/</t>
         </is>
@@ -2950,7 +3875,22 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35633553/</t>
         </is>
@@ -2991,7 +3931,22 @@
           <t>2024-04-19</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35917137/</t>
         </is>
@@ -3032,7 +3987,22 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1873359/</t>
         </is>
@@ -3073,7 +4043,22 @@
           <t>2014-07-10</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25845586/</t>
         </is>
@@ -3114,7 +4099,22 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3174543/</t>
         </is>
@@ -3155,7 +4155,22 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2068188/</t>
         </is>
@@ -3196,7 +4211,22 @@
           <t>2006-01-31</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1461181/</t>
         </is>
@@ -3237,7 +4267,22 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1772702/</t>
         </is>
@@ -3278,7 +4323,22 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33973077/</t>
         </is>
@@ -3319,7 +4379,22 @@
           <t>2013-12-06</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5997849/</t>
         </is>
@@ -3360,7 +4435,22 @@
           <t>2013-07-12</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/23249761/</t>
         </is>
@@ -3401,7 +4491,22 @@
           <t>2019-01-11</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30377785/</t>
         </is>
@@ -3442,7 +4547,22 @@
           <t>2008-05-09</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3024072/</t>
         </is>
@@ -3483,7 +4603,22 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1482692/</t>
         </is>
@@ -3524,7 +4659,22 @@
           <t>2011-08-11</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6389522/</t>
         </is>
@@ -3565,7 +4715,22 @@
           <t>2014-01-31</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25785314/</t>
         </is>
@@ -3606,7 +4771,22 @@
           <t>2005-05-08</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1419661/</t>
         </is>
@@ -3647,7 +4827,22 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2270501/</t>
         </is>
@@ -3688,7 +4883,22 @@
           <t>1998-11-08</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2157280/</t>
         </is>
@@ -3729,7 +4939,22 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35470200/</t>
         </is>
@@ -3770,7 +4995,22 @@
           <t>2018-06-15</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26845720/</t>
         </is>
@@ -3811,7 +5051,22 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2372541/</t>
         </is>
@@ -3852,7 +5107,22 @@
           <t>2022-01-08</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35392460/</t>
         </is>
@@ -3893,7 +5163,22 @@
           <t>2011-09-02</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/7055665/</t>
         </is>
@@ -3934,7 +5219,22 @@
           <t>2021-01-15</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34834554/</t>
         </is>
@@ -3975,7 +5275,22 @@
           <t>2006-03-30</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2006926/</t>
         </is>
@@ -4016,7 +5331,22 @@
           <t>1979</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2405664/</t>
         </is>
@@ -4057,7 +5387,22 @@
           <t>2000-08-23</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1424212/</t>
         </is>
@@ -4098,7 +5443,22 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1301943/</t>
         </is>
@@ -4139,7 +5499,22 @@
           <t>2012-11-16</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20388613/</t>
         </is>
@@ -4180,7 +5555,22 @@
           <t>2019-06-01</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>1</v>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33403736/</t>
         </is>
@@ -4221,7 +5611,22 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1513408/</t>
         </is>
@@ -4262,7 +5667,22 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1940694/</t>
         </is>
@@ -4303,7 +5723,22 @@
           <t>2022-10-11</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36088962/</t>
         </is>
@@ -4344,7 +5779,22 @@
           <t>2007-10-01</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2130046/</t>
         </is>
@@ -4385,7 +5835,22 @@
           <t>2012-07-05</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10727042/</t>
         </is>
@@ -4426,7 +5891,22 @@
           <t>2016-03-09</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26890949/</t>
         </is>
@@ -4467,7 +5947,22 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1433367/</t>
         </is>
@@ -4508,7 +6003,22 @@
           <t>2023-05-25</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30414283/</t>
         </is>
@@ -4549,7 +6059,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1482701/</t>
         </is>
@@ -4590,7 +6115,22 @@
           <t>1960-05-26</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308405/</t>
         </is>
@@ -4627,7 +6167,22 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3215506/</t>
         </is>
@@ -4668,7 +6223,22 @@
           <t>2013-01-25</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20416699/</t>
         </is>
@@ -4709,7 +6279,22 @@
           <t>2019-10-07</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33447759/</t>
         </is>
@@ -4750,7 +6335,22 @@
           <t>2015-07-23</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26379074/</t>
         </is>
@@ -4791,7 +6391,22 @@
           <t>2018-01-16</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26628256/</t>
         </is>
@@ -4832,7 +6447,22 @@
           <t>2020-02-14</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33434848/</t>
         </is>
@@ -4873,7 +6503,22 @@
           <t>1988</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1897072/</t>
         </is>
@@ -4914,7 +6559,22 @@
           <t>2022-10-01</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36035677/</t>
         </is>
@@ -4955,7 +6615,22 @@
           <t>2016-08-20</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26891306/</t>
         </is>
@@ -4996,7 +6671,22 @@
           <t>2018-02-02</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27621546/</t>
         </is>
@@ -5037,7 +6727,22 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1916915/</t>
         </is>
@@ -5078,7 +6783,22 @@
           <t>2020-10-07</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35211536/</t>
         </is>
@@ -5119,7 +6839,22 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25847406/</t>
         </is>
@@ -5160,7 +6895,22 @@
           <t>2012-06-16</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10767851/</t>
         </is>
@@ -5201,7 +6951,22 @@
           <t>2019-11-20</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30185523/</t>
         </is>
@@ -5242,7 +7007,22 @@
           <t>2014-09-26</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25966045/</t>
         </is>
@@ -5283,7 +7063,22 @@
           <t>2021-07-24</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>1</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35445373/</t>
         </is>
@@ -5324,7 +7119,22 @@
           <t>2010-06-12</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1</v>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4804511/</t>
         </is>
@@ -5365,7 +7175,22 @@
           <t>2017-01-09</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26891314/</t>
         </is>
@@ -5406,7 +7231,22 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1864713/</t>
         </is>
@@ -5447,7 +7287,22 @@
           <t>1963</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20266727/</t>
         </is>
@@ -5488,7 +7343,22 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3324504/</t>
         </is>
@@ -5529,7 +7399,22 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5256306/</t>
         </is>
@@ -5570,7 +7455,22 @@
           <t>2016-06-01</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26890963/</t>
         </is>
@@ -5611,7 +7511,22 @@
           <t>2009-08-29</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>1</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4116941/</t>
         </is>
@@ -5652,7 +7567,22 @@
           <t>2002-07-10</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1416860/</t>
         </is>
@@ -5693,7 +7623,22 @@
           <t>2018-08-24</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>1</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30263969/</t>
         </is>
@@ -5734,7 +7679,22 @@
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6733088/</t>
         </is>
@@ -5775,7 +7735,22 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3037321/</t>
         </is>
@@ -5816,7 +7791,22 @@
           <t>1936</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2057491/</t>
         </is>
@@ -5857,7 +7847,22 @@
           <t>2009-11-20</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3892235/</t>
         </is>
@@ -5894,7 +7899,22 @@
           <t>1973</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2238704/</t>
         </is>
@@ -5935,7 +7955,22 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2244784/</t>
         </is>
@@ -5976,7 +8011,22 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3062995/</t>
         </is>
@@ -6017,7 +8067,22 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19967498/</t>
         </is>
@@ -6058,7 +8123,22 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2287322/</t>
         </is>
@@ -6099,7 +8179,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3008923/</t>
         </is>
@@ -6140,7 +8235,22 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3145154/</t>
         </is>
@@ -6181,7 +8291,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464545/</t>
         </is>
@@ -6222,7 +8347,22 @@
           <t>2019-08-02</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>1</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30449240/</t>
         </is>
@@ -6263,7 +8403,22 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1963568/</t>
         </is>
@@ -6300,7 +8455,22 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6527259/</t>
         </is>
@@ -6341,7 +8511,22 @@
           <t>1978</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3018465/</t>
         </is>
@@ -6382,7 +8567,22 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10472763/</t>
         </is>
@@ -6423,7 +8623,22 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3145148/</t>
         </is>
@@ -6464,7 +8679,22 @@
           <t>1993-09-15</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1401228/</t>
         </is>
@@ -6501,7 +8731,22 @@
           <t>2016-08-18</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26855721/</t>
         </is>
@@ -6542,7 +8787,22 @@
           <t>2014-01-23</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25791073/</t>
         </is>
@@ -6583,7 +8843,22 @@
           <t>2015-02-19</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25951736/</t>
         </is>
@@ -6624,7 +8899,22 @@
           <t>2018-07-06</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30198729/</t>
         </is>
@@ -6665,7 +8955,22 @@
           <t>2011-01-27</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5384872/</t>
         </is>
@@ -6706,7 +9011,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2281702/</t>
         </is>
@@ -6747,7 +9067,22 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464578/</t>
         </is>
@@ -6788,7 +9123,22 @@
           <t>2021-05-01</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35026731/</t>
         </is>
@@ -6829,7 +9179,22 @@
           <t>2017-08-18</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26969037/</t>
         </is>
@@ -6870,7 +9235,22 @@
           <t>2008-03-29</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>1</v>
+      </c>
+      <c r="N158" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2567628/</t>
         </is>
@@ -6911,7 +9291,22 @@
           <t>2014-09-16</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24521773/</t>
         </is>
@@ -6952,7 +9347,22 @@
           <t>2010-11-06</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>1</v>
+      </c>
+      <c r="N160" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4917723/</t>
         </is>
@@ -6993,7 +9403,22 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3271513/</t>
         </is>
@@ -7034,7 +9459,22 @@
           <t>2017-09-09</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>1</v>
+      </c>
+      <c r="N162" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27069788/</t>
         </is>
@@ -7075,7 +9515,22 @@
           <t>2013-01-31</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20369263/</t>
         </is>
@@ -7116,7 +9571,22 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3070711/</t>
         </is>
@@ -7157,7 +9627,22 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25837721/</t>
         </is>
@@ -7198,7 +9683,22 @@
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>1</v>
+      </c>
+      <c r="N166" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/37006326/</t>
         </is>
@@ -7239,7 +9739,22 @@
           <t>2015-07-23</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26318077/</t>
         </is>
@@ -7280,7 +9795,22 @@
           <t>2006-04-04</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3240885/</t>
         </is>
@@ -7321,7 +9851,22 @@
           <t>2015-08-07</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26268610/</t>
         </is>
@@ -7358,7 +9903,22 @@
           <t>2008-05-30</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3087564/</t>
         </is>
@@ -7399,7 +9959,22 @@
           <t>2017-10-14</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>1</v>
+      </c>
+      <c r="N171" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27173314/</t>
         </is>
@@ -7440,7 +10015,22 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25981824/</t>
         </is>
@@ -7481,7 +10071,22 @@
           <t>2016-04-30</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25857434/</t>
         </is>
@@ -7522,7 +10127,22 @@
           <t>2024-04-12</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34436818/</t>
         </is>
@@ -7563,7 +10183,22 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26933219/</t>
         </is>
@@ -7604,7 +10239,22 @@
           <t>2017-07-14</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26747836/</t>
         </is>
@@ -7645,7 +10295,22 @@
           <t>2013-01-25</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19977815/</t>
         </is>
@@ -7686,7 +10351,22 @@
           <t>2013-05-31</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24325876/</t>
         </is>
@@ -7727,7 +10407,22 @@
           <t>2015-02-18</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26782692/</t>
         </is>
@@ -7768,7 +10463,22 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35168646/</t>
         </is>
@@ -7809,7 +10519,22 @@
           <t>2010-09-22</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5044746/</t>
         </is>
@@ -7850,7 +10575,22 @@
           <t>2021-09-19</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>1</v>
+      </c>
+      <c r="N182" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26754627/</t>
         </is>
@@ -7891,7 +10631,22 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3406827/</t>
         </is>
@@ -7932,7 +10687,22 @@
           <t>2015-01-01</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25978333/</t>
         </is>
@@ -7973,7 +10743,22 @@
           <t>2009-07-03</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3737278/</t>
         </is>
@@ -8014,7 +10799,22 @@
           <t>2016-07-02</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26802090/</t>
         </is>
@@ -8055,7 +10855,22 @@
           <t>2017-01-24</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26628239/</t>
         </is>
@@ -8096,7 +10911,22 @@
           <t>2015-04-03</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25769893/</t>
         </is>
@@ -8137,7 +10967,22 @@
           <t>2019-02-05</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
+      <c r="I189" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30295908/</t>
         </is>
@@ -8178,7 +11023,22 @@
           <t>2013-04-28</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>1</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19977818/</t>
         </is>
@@ -8219,7 +11079,22 @@
           <t>2011-02-03</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
+      <c r="I191" t="n">
+        <v>1</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4913184/</t>
         </is>
@@ -8260,7 +11135,22 @@
           <t>2012-03-23</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6523584/</t>
         </is>
@@ -8301,7 +11191,22 @@
           <t>2016-12-17</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>1</v>
+      </c>
+      <c r="N193" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26831514/</t>
         </is>
@@ -8342,7 +11247,22 @@
           <t>2016-10-04</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26860477/</t>
         </is>
@@ -8383,7 +11303,22 @@
           <t>2014-05-30</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25869685/</t>
         </is>
@@ -8424,7 +11359,22 @@
           <t>2016-10-03</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26847189/</t>
         </is>
@@ -8465,7 +11415,22 @@
           <t>2017-09-16</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>1</v>
+      </c>
+      <c r="N197" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27133167/</t>
         </is>
@@ -8506,7 +11471,22 @@
           <t>2013-08-15</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24706750/</t>
         </is>
@@ -8547,7 +11527,22 @@
           <t>2015-05-30</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>1</v>
+      </c>
+      <c r="N199" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26384719/</t>
         </is>
@@ -8588,7 +11583,22 @@
           <t>2016-01-22</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26677940/</t>
         </is>
@@ -8629,7 +11639,22 @@
           <t>2013-05-24</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/21323597/</t>
         </is>
@@ -8670,7 +11695,22 @@
           <t>2015-10-17</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>1</v>
+      </c>
+      <c r="N202" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26628447/</t>
         </is>
@@ -8711,7 +11751,22 @@
           <t>2013-06-01</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>1</v>
+      </c>
+      <c r="N203" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20429112/</t>
         </is>
@@ -8752,7 +11807,22 @@
           <t>2015-04-30</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>1</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25745849/</t>
         </is>
